--- a/output/pdf_financials_xlsx/URL.xlsx
+++ b/output/pdf_financials_xlsx/URL.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/URL.xlsx
+++ b/output/pdf_financials_xlsx/URL.xlsx
@@ -429,12 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,10 +453,15 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
@@ -475,9 +481,12 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>48.962799</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>55.233043</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>65.468311</v>
       </c>
     </row>
@@ -488,10 +497,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-43.152984</v>
+        <v>40.083586</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>-48.735851</v>
+        <v>43.152984</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>48.735851</v>
       </c>
     </row>
     <row r="6">
@@ -501,9 +513,12 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>8.879213</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>12.080059</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>16.73246</v>
       </c>
     </row>
@@ -514,9 +529,12 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>0.8496089999999999</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>1.046766</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>1.095916</v>
       </c>
     </row>
@@ -532,6 +550,9 @@
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -540,10 +561,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.225953</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.465319</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.346849</v>
       </c>
     </row>
     <row r="10">
@@ -553,9 +577,12 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>7.010865</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>8.002348</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>8.897907</v>
       </c>
     </row>
@@ -566,9 +593,12 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>1.868348</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>4.077711</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>7.834553</v>
       </c>
     </row>
@@ -584,6 +614,9 @@
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -592,10 +625,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -610,6 +646,9 @@
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -618,9 +657,12 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-0.705124</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-1.691705</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-0.9700490000000001</v>
       </c>
     </row>
@@ -631,9 +673,12 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-1.710775</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>1.280294</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>4.738409</v>
       </c>
     </row>
@@ -644,10 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.9754159999999999</v>
+        <v>-0.426137</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-2.546148</v>
+        <v>0.9754159999999999</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>2.546148</v>
       </c>
     </row>
     <row r="18">
@@ -666,6 +714,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -683,6 +736,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -691,9 +749,12 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-1.284638</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>0.304878</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>2.192261</v>
       </c>
     </row>
@@ -709,6 +770,9 @@
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -717,9 +781,12 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-0.529863</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-0.648015</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-1.240422</v>
       </c>
     </row>
@@ -730,9 +797,12 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-1.284638</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>0.304878</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>2.192261</v>
       </c>
     </row>
@@ -743,9 +813,12 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -756,9 +829,12 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -773,7 +849,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>109.61305</v>
       </c>
     </row>
@@ -784,9 +865,12 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-1.710775</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>1.280294</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>4.738409</v>
       </c>
     </row>
@@ -802,6 +886,9 @@
       <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -810,9 +897,12 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-1.710775</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>1.280294</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>4.738409</v>
       </c>
     </row>
@@ -823,9 +913,12 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-3.494030233034676</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>2.317985630449512</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>7.237713830741716</v>
       </c>
     </row>
@@ -836,9 +929,12 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-24.90900322953048</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>76.1868758269585</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>53.73423864423692</v>
       </c>
     </row>
@@ -849,9 +945,12 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-2.623702129447297</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>0.5519847964922012</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>3.348583408544021</v>
       </c>
     </row>
@@ -869,9 +968,12 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>2.379275</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>3.003106</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>3.600332</v>
       </c>
     </row>
@@ -887,6 +989,9 @@
       <c r="C35" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -895,9 +1000,12 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>2.379275</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>3.003106</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>3.600332</v>
       </c>
     </row>
@@ -913,6 +1021,9 @@
       <c r="C37" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -921,9 +1032,12 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>0.54889</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>0.53912</v>
       </c>
     </row>
@@ -939,6 +1053,9 @@
       <c r="C39" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -952,6 +1069,9 @@
       <c r="C40" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -960,9 +1080,12 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>0.114505</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>0.416791</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>0.40988</v>
       </c>
     </row>
@@ -978,6 +1101,9 @@
       <c r="C42" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -991,6 +1117,9 @@
       <c r="C43" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1004,6 +1133,9 @@
       <c r="C44" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -1017,6 +1149,9 @@
       <c r="C45" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1030,6 +1165,9 @@
       <c r="C46" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -1043,6 +1181,9 @@
       <c r="C47" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1051,9 +1192,12 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>23.568839</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>26.719233</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>29.044491</v>
       </c>
     </row>
@@ -1064,9 +1208,12 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>26.062619</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>30.13913</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>33.054703</v>
       </c>
     </row>
@@ -1077,9 +1224,12 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>2.562123</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>1.475029</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>1.086334</v>
       </c>
     </row>
@@ -1095,6 +1245,9 @@
       <c r="C51" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -1108,6 +1261,9 @@
       <c r="C52" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -1116,9 +1272,12 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.06464399999999999</v>
       </c>
       <c r="C53" s="3" t="n">
+        <v>0.107734</v>
+      </c>
+      <c r="D53" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1134,6 +1293,9 @@
       <c r="C54" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1151,6 +1313,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -1164,6 +1331,9 @@
       <c r="C56" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -1177,6 +1347,9 @@
       <c r="C57" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -1185,9 +1358,12 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>0.107734</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>1.198672</v>
       </c>
     </row>
@@ -1198,9 +1374,12 @@
         </is>
       </c>
       <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
         <v>0.174221</v>
       </c>
-      <c r="C59" s="3" t="n">
+      <c r="D59" s="3" t="n">
         <v>2.188175</v>
       </c>
     </row>
@@ -1211,9 +1390,12 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
+        <v>8.065288000000001</v>
+      </c>
+      <c r="C60" s="3" t="n">
         <v>8.774492</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="D60" s="3" t="n">
         <v>9.186024</v>
       </c>
     </row>
@@ -1229,6 +1411,9 @@
       <c r="C61" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -1246,6 +1431,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -1263,6 +1453,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -1276,6 +1471,9 @@
       <c r="C64" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1289,6 +1487,9 @@
       <c r="C65" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1302,6 +1503,9 @@
       <c r="C66" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -1315,6 +1519,9 @@
       <c r="C67" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -1323,9 +1530,12 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
+        <v>6.132728</v>
+      </c>
+      <c r="C68" s="3" t="n">
         <v>8.797833000000001</v>
       </c>
-      <c r="C68" s="3" t="n">
+      <c r="D68" s="3" t="n">
         <v>11.028679</v>
       </c>
     </row>
@@ -1339,6 +1549,9 @@
         <v>0</v>
       </c>
       <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
         <v>0.08264299999999999</v>
       </c>
     </row>
@@ -1354,6 +1567,9 @@
       <c r="C70" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -1365,6 +1581,9 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
         <v>0.08264299999999999</v>
       </c>
     </row>
@@ -1380,6 +1599,9 @@
       <c r="C72" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -1393,6 +1615,9 @@
       <c r="C73" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -1406,6 +1631,9 @@
       <c r="C74" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -1414,9 +1642,12 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
+        <v>31.716423</v>
+      </c>
+      <c r="C75" s="3" t="n">
         <v>35.141299</v>
       </c>
-      <c r="C75" s="3" t="n">
+      <c r="D75" s="3" t="n">
         <v>36.751871</v>
       </c>
     </row>
@@ -1427,9 +1658,12 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
+        <v>37.849151</v>
+      </c>
+      <c r="C76" s="3" t="n">
         <v>43.939132</v>
       </c>
-      <c r="C76" s="3" t="n">
+      <c r="D76" s="3" t="n">
         <v>47.863193</v>
       </c>
     </row>
@@ -1445,6 +1679,9 @@
       <c r="C77" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -1458,6 +1695,9 @@
       <c r="C78" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -1471,6 +1711,9 @@
       <c r="C79" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -1483,7 +1726,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C80" s="3" t="n">
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
         <v>0.04846789763463663</v>
       </c>
     </row>
@@ -1499,6 +1747,9 @@
       <c r="C81" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -1512,6 +1763,9 @@
       <c r="C82" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -1525,6 +1779,9 @@
       <c r="C83" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -1538,6 +1795,9 @@
       <c r="C84" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -1551,6 +1811,9 @@
       <c r="C85" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -1568,6 +1831,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -1585,6 +1853,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -1593,9 +1866,12 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
+        <v>34.480957</v>
+      </c>
+      <c r="C88" s="3" t="n">
         <v>34.156623</v>
       </c>
-      <c r="C88" s="3" t="n">
+      <c r="D88" s="3" t="n">
         <v>33.782742</v>
       </c>
     </row>
@@ -1611,6 +1887,9 @@
       <c r="C89" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -1619,9 +1898,12 @@
         </is>
       </c>
       <c r="B90" s="3" t="n">
+        <v>-35.300832</v>
+      </c>
+      <c r="C90" s="3" t="n">
         <v>-35.643969</v>
       </c>
-      <c r="C90" s="3" t="n">
+      <c r="D90" s="3" t="n">
         <v>-34.69213</v>
       </c>
     </row>
@@ -1632,9 +1914,12 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
+        <v>-0.048718</v>
+      </c>
+      <c r="C91" s="3" t="n">
         <v>-0.242706</v>
       </c>
-      <c r="C91" s="3" t="n">
+      <c r="D91" s="3" t="n">
         <v>-0.03169</v>
       </c>
     </row>
@@ -1645,9 +1930,12 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
+        <v>2.545187</v>
+      </c>
+      <c r="C92" s="3" t="n">
         <v>3.218713</v>
       </c>
-      <c r="C92" s="3" t="n">
+      <c r="D92" s="3" t="n">
         <v>4.50214</v>
       </c>
     </row>
@@ -1663,6 +1951,9 @@
       <c r="C93" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -1671,9 +1962,12 @@
         </is>
       </c>
       <c r="B94" s="3" t="n">
+        <v>2.427645</v>
+      </c>
+      <c r="C94" s="3" t="n">
         <v>0.884116</v>
       </c>
-      <c r="C94" s="3" t="n">
+      <c r="D94" s="3" t="n">
         <v>2.640889</v>
       </c>
     </row>
@@ -1684,9 +1978,12 @@
         </is>
       </c>
       <c r="B95" s="3" t="n">
+        <v>0.169337</v>
+      </c>
+      <c r="C95" s="3" t="n">
         <v>-0.620153</v>
       </c>
-      <c r="C95" s="3" t="n">
+      <c r="D95" s="3" t="n">
         <v>-0.935781</v>
       </c>
     </row>
@@ -1697,9 +1994,12 @@
         </is>
       </c>
       <c r="B96" s="3" t="n">
+        <v>2.596982</v>
+      </c>
+      <c r="C96" s="3" t="n">
         <v>0.263963</v>
       </c>
-      <c r="C96" s="3" t="n">
+      <c r="D96" s="3" t="n">
         <v>1.705108</v>
       </c>
     </row>
@@ -1719,6 +2019,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -1733,10 +2038,15 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="3" t="n">
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
         <v>0.304878</v>
       </c>
-      <c r="C99" s="3" t="n">
+      <c r="D99" s="3" t="n">
         <v>2.192261</v>
       </c>
     </row>
@@ -1746,10 +2056,15 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="3" t="n">
-        <v>0</v>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1759,10 +2074,15 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="3" t="n">
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
         <v>-0.302286</v>
       </c>
-      <c r="C101" s="3" t="n">
+      <c r="D101" s="3" t="n">
         <v>0.558439</v>
       </c>
     </row>
@@ -1772,10 +2092,15 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="3" t="n">
-        <v>0</v>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1785,10 +2110,15 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="3" t="n">
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
         <v>-0.121541</v>
       </c>
-      <c r="C103" s="3" t="n">
+      <c r="D103" s="3" t="n">
         <v>-0.107756</v>
       </c>
     </row>
@@ -1798,10 +2128,15 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="3" t="n">
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
         <v>2.033109</v>
       </c>
-      <c r="C104" s="3" t="n">
+      <c r="D104" s="3" t="n">
         <v>2.145001</v>
       </c>
     </row>
@@ -1811,10 +2146,15 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="3" t="n">
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
         <v>2.757112</v>
       </c>
-      <c r="C105" s="3" t="n">
+      <c r="D105" s="3" t="n">
         <v>2.828289</v>
       </c>
     </row>
@@ -1824,10 +2164,15 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="3" t="n">
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
         <v>4.366394</v>
       </c>
-      <c r="C106" s="3" t="n">
+      <c r="D106" s="3" t="n">
         <v>5.423973</v>
       </c>
     </row>
@@ -1837,10 +2182,15 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="3" t="n">
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
         <v>0.10742</v>
       </c>
-      <c r="C107" s="3" t="n">
+      <c r="D107" s="3" t="n">
         <v>1.307359</v>
       </c>
     </row>
@@ -1850,10 +2200,15 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="3" t="n">
-        <v>0</v>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1863,10 +2218,15 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="3" t="n">
-        <v>0</v>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1876,10 +2236,15 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="3" t="n">
-        <v>0</v>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1889,10 +2254,15 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="3" t="n">
-        <v>0</v>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1902,10 +2272,15 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="3" t="n">
-        <v>0</v>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1915,10 +2290,15 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="3" t="n">
-        <v>0</v>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1928,10 +2308,15 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="3" t="n">
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
         <v>-0.792408</v>
       </c>
-      <c r="C114" s="3" t="n">
+      <c r="D114" s="3" t="n">
         <v>-0.971982</v>
       </c>
     </row>
@@ -1941,10 +2326,15 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="3" t="n">
+      <c r="B115" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="n">
         <v>0.584221</v>
       </c>
-      <c r="C115" s="3" t="n">
+      <c r="D115" s="3" t="n">
         <v>0.008722000000000001</v>
       </c>
     </row>
@@ -1954,10 +2344,15 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="3" t="n">
-        <v>0</v>
+      <c r="B116" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1967,10 +2362,15 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="3" t="n">
-        <v>0</v>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1980,10 +2380,15 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="3" t="n">
-        <v>0</v>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1993,10 +2398,15 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="3" t="n">
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
         <v>-0.845751</v>
       </c>
-      <c r="C119" s="3" t="n">
+      <c r="D119" s="3" t="n">
         <v>-6.370154</v>
       </c>
     </row>
@@ -2006,10 +2416,15 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="3" t="n">
-        <v>0</v>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2019,10 +2434,15 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="3" t="n">
-        <v>0</v>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2032,10 +2452,15 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="3" t="n">
-        <v>0</v>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2045,10 +2470,15 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="3" t="n">
-        <v>0</v>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2058,10 +2488,15 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="3" t="n">
-        <v>0</v>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2071,10 +2506,15 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="3" t="n">
-        <v>0</v>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2084,10 +2524,15 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="3" t="n">
-        <v>0</v>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2107,6 +2552,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -2114,10 +2564,15 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="3" t="n">
-        <v>0</v>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2127,10 +2582,15 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="3" t="n">
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="n">
         <v>-5.221518</v>
       </c>
-      <c r="C129" s="3" t="n">
+      <c r="D129" s="3" t="n">
         <v>-2.547154</v>
       </c>
     </row>
@@ -2140,10 +2600,15 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="3" t="n">
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
         <v>2.379275</v>
       </c>
-      <c r="C130" s="3" t="n">
+      <c r="D130" s="3" t="n">
         <v>3.003106</v>
       </c>
     </row>
@@ -2153,10 +2618,15 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="3" t="n">
-        <v>0</v>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2166,10 +2636,15 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="3" t="n">
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
         <v>0.623831</v>
       </c>
-      <c r="C132" s="3" t="n">
+      <c r="D132" s="3" t="n">
         <v>0.597226</v>
       </c>
     </row>
@@ -2179,10 +2654,15 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="3" t="n">
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
         <v>3.003106</v>
       </c>
-      <c r="C133" s="3" t="n">
+      <c r="D133" s="3" t="n">
         <v>3.600332</v>
       </c>
     </row>
@@ -2192,10 +2672,15 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="3" t="n">
-        <v>0</v>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2205,10 +2690,15 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="3" t="n">
+      <c r="B135" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n">
         <v>6.635791</v>
       </c>
-      <c r="C135" s="3" t="n">
+      <c r="D135" s="3" t="n">
         <v>9.736395</v>
       </c>
     </row>
@@ -2223,7 +2713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2255,10 +2745,15 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -2286,9 +2781,12 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
+        <v>2.379275</v>
+      </c>
+      <c r="F2" s="5" t="n">
         <v>3.003106</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="G2" s="5" t="n">
         <v>3.600332</v>
       </c>
     </row>
@@ -2314,9 +2812,12 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
+        <v>0.114505</v>
+      </c>
+      <c r="F3" s="5" t="n">
         <v>0.416791</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="G3" s="5" t="n">
         <v>0.40988</v>
       </c>
     </row>
@@ -2342,9 +2843,12 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
+        <v>0.005031</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>0.126572</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="G4" s="5" t="n">
         <v>0.238185</v>
       </c>
     </row>
@@ -2370,7 +2874,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -2392,9 +2901,12 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="5" t="n">
+        <v>2.983795</v>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>2.462386</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="G6" s="5" t="n">
         <v>2.018313</v>
       </c>
     </row>
@@ -2416,9 +2928,12 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="5" t="n">
+        <v>20.580013</v>
+      </c>
+      <c r="F7" s="5" t="n">
         <v>24.130275</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="G7" s="5" t="n">
         <v>24.987993</v>
       </c>
     </row>
@@ -2444,9 +2959,12 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
+        <v>26.062619</v>
+      </c>
+      <c r="F8" s="5" t="n">
         <v>30.13913</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="G8" s="5" t="n">
         <v>33.054703</v>
       </c>
     </row>
@@ -2468,9 +2986,12 @@
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" s="5" t="n">
+        <v>1.081316</v>
+      </c>
+      <c r="F9" s="5" t="n">
         <v>1.101474</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="G9" s="5" t="n">
         <v>1.03733</v>
       </c>
     </row>
@@ -2492,9 +3013,12 @@
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" s="5" t="n">
+        <v>0.158908</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>1.06391</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="G10" s="5" t="n">
         <v>1.633383</v>
       </c>
     </row>
@@ -2520,9 +3044,12 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
+        <v>2.562123</v>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>1.475029</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="G11" s="5" t="n">
         <v>1.086334</v>
       </c>
     </row>
@@ -2543,10 +3070,15 @@
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" s="5" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>0.099999</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <v>0.7475000000000001</v>
       </c>
     </row>
@@ -2571,10 +3103,15 @@
           <t>NotesReceivable</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>0.54889</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="G13" s="5" t="n">
         <v>0.53912</v>
       </c>
     </row>
@@ -2595,10 +3132,15 @@
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" s="5" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>0.146142</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>0.138471</v>
       </c>
     </row>
@@ -2619,10 +3161,15 @@
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" s="5" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
         <v>1.350673</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="G15" s="5" t="n">
         <v>0.918815</v>
       </c>
     </row>
@@ -2647,10 +3194,15 @@
           <t>NetPPE</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n">
         <v>0.107734</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>1.198672</v>
       </c>
     </row>
@@ -2675,10 +3227,15 @@
           <t>OtherIntangibleAssets</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n">
         <v>0.174221</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="G17" s="5" t="n">
         <v>2.188175</v>
       </c>
     </row>
@@ -2700,9 +3257,12 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" s="5" t="n">
+        <v>1.533193</v>
+      </c>
+      <c r="F18" s="5" t="n">
         <v>0.614529</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2730,9 +3290,12 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
+        <v>8.065288000000001</v>
+      </c>
+      <c r="F19" s="5" t="n">
         <v>8.774492</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="G19" s="5" t="n">
         <v>9.186024</v>
       </c>
     </row>
@@ -2753,10 +3316,15 @@
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" s="5" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n">
         <v>0.5593050000000001</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="G20" s="5" t="n">
         <v>0.560134</v>
       </c>
     </row>
@@ -2781,10 +3349,15 @@
           <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n">
         <v>8.797833000000001</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="G21" s="5" t="n">
         <v>11.028679</v>
       </c>
     </row>
@@ -2806,9 +3379,12 @@
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" s="5" t="n">
+        <v>3.043598</v>
+      </c>
+      <c r="F22" s="5" t="n">
         <v>4.583534</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="G22" s="5" t="n">
         <v>5.205486</v>
       </c>
     </row>
@@ -2829,10 +3405,15 @@
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" s="5" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n">
         <v>30.138387</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="G23" s="5" t="n">
         <v>31.470576</v>
       </c>
     </row>
@@ -2853,10 +3434,15 @@
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" s="5" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
         <v>0.419378</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2888,7 +3474,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
         <v>0.08264299999999999</v>
       </c>
     </row>
@@ -2914,7 +3505,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
         <v>0.075809</v>
       </c>
     </row>
@@ -2940,9 +3536,12 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
+        <v>37.849151</v>
+      </c>
+      <c r="F27" s="5" t="n">
         <v>43.939132</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="G27" s="5" t="n">
         <v>47.863193</v>
       </c>
     </row>
@@ -2963,10 +3562,15 @@
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" s="5" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n">
         <v>1.33228</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="G28" s="5" t="n">
         <v>1.279532</v>
       </c>
     </row>
@@ -2992,7 +3596,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n">
         <v>0.505047</v>
       </c>
     </row>
@@ -3017,10 +3626,15 @@
           <t>CapitalStock</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
         <v>34.156623</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="G30" s="5" t="n">
         <v>33.782742</v>
       </c>
     </row>
@@ -3047,6 +3661,9 @@
       <c r="F31" s="5" t="n">
         <v>0.015608</v>
       </c>
+      <c r="G31" s="5" t="n">
+        <v>0.015608</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3069,10 +3686,15 @@
           <t>AdditionalPaidInCapital</t>
         </is>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n">
         <v>3.218713</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="G32" s="5" t="n">
         <v>4.50214</v>
       </c>
     </row>
@@ -3098,9 +3720,12 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
+        <v>-0.048718</v>
+      </c>
+      <c r="F33" s="5" t="n">
         <v>-0.242706</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="G33" s="5" t="n">
         <v>-0.03169</v>
       </c>
     </row>
@@ -3126,9 +3751,12 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
+        <v>-35.300832</v>
+      </c>
+      <c r="F34" s="5" t="n">
         <v>-35.643969</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="G34" s="5" t="n">
         <v>-34.69213</v>
       </c>
     </row>
@@ -3150,9 +3778,12 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="5" t="n">
+        <v>2.258308</v>
+      </c>
+      <c r="F35" s="5" t="n">
         <v>1.504269</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="G35" s="5" t="n">
         <v>3.57667</v>
       </c>
     </row>
@@ -3178,9 +3809,12 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
+        <v>0.169337</v>
+      </c>
+      <c r="F36" s="5" t="n">
         <v>-0.620153</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="G36" s="5" t="n">
         <v>-0.935781</v>
       </c>
     </row>
@@ -3206,394 +3840,486 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
+        <v>2.427645</v>
+      </c>
+      <c r="F37" s="5" t="n">
         <v>0.884116</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="G37" s="5" t="n">
         <v>2.640889</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Net income for the year</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>0.304878</v>
+          <t>Convertible debenture receivable 6</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>2.192261</v>
+        <v>0.099999</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Adjustment for items not involving cash</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Accretion expense</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" s="5" t="n">
-        <v>0.219919</v>
+          <t>Promissory notes receivable 7, 8, 20</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NotesReceivable</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.082312</v>
+        <v>0.54889</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Adjustment for items not involving cash</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>1.015601</v>
+          <t>Investment in joint venture 7</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.7758659999999999</v>
+        <v>0.146142</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Adjustment for items not involving cash</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (recovery)</t>
+          <t>Investment in associates 8</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" s="5" t="n">
-        <v>-0.1359</v>
+        <v>1.66109</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.042646</v>
+        <v>1.350673</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Adjustment for items not involving cash</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Equipment 9</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0.06464399999999999</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-0.060129</v>
+        <v>0.107734</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Adjustment for items not involving cash</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Loss on investments</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" s="5" t="n">
-        <v>0.50292</v>
+          <t>Other intangible assets 10</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>OtherIntangibleAssets</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.5401010000000001</v>
+        <v>0.174221</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Adjustment for items not involving cash</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Realized gain on digital currency</t>
+          <t>Deferred income tax asset 25</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="5" t="n">
-        <v>-1.073739</v>
+        <v>0.382883</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>-1.214867</v>
+        <v>0.5593050000000001</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Adjustment for items not involving cash</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Share of loss from investment in joint venture</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities 14, 20</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
-        <v>0.321469</v>
+        <v>6.132728</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.619378</v>
+        <v>8.797833000000001</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Adjustment for items not involving cash</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Loss from equity pick-up</t>
+          <t>Deferred revenue, current portion 15</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>0.635167</v>
+        <v>24.969653</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.757356</v>
+        <v>30.138387</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Adjustment for items not involving cash</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fair value of shares issued as finder’s fees for business combination</t>
+          <t>Convertible debenture – liability portion 16</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>0.111038</v>
+      <c r="E47" s="5" t="n">
+        <v>3.703172</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Adjustment for items not involving cash</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Share-based payment</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>0.10742</v>
+          <t>Promissory note payable 17</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>1.307359</v>
+        <v>0.419378</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Adjustment for items not involving cash</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Adjustment for items not involving cash total</t>
+          <t>Deferred revenue, long-term portion 15</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>1.897735</v>
+        <v>1.295268</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>5.153321</v>
+        <v>1.33228</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital related to operations</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Receivables</t>
+          <t>Share capital 18</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>-0.302286</v>
+        <v>34.480957</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.558439</v>
+        <v>34.156623</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital related to operations</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Convertible debt – equity portion 16</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" s="5" t="n">
-        <v>-0.121541</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>-0.107756</v>
+        <v>0.566106</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital related to operations</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Registry deposits</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Contributed surplus 18</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
-        <v>0.746143</v>
+        <v>2.545187</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.333685</v>
+        <v>3.218713</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -3604,20 +4330,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital related to operations</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Prepaid domain name registry fees</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
-        <v>-1.585685</v>
+          <t>Net income for the year</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>-2.030761</v>
+        <v>0.304878</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>2.192261</v>
       </c>
     </row>
     <row r="54">
@@ -3628,24 +4363,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital related to operations</t>
+          <t>Adjustment for items not involving cash</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>2.033109</v>
+          <t>Accretion expense</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>2.145001</v>
+        <v>0.219919</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.082312</v>
       </c>
     </row>
     <row r="55">
@@ -3656,20 +4392,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital related to operations</t>
+          <t>Adjustment for items not involving cash</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Customer deposits</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" s="5" t="n">
-        <v>1.211204</v>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.856177</v>
+        <v>1.015601</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.7758659999999999</v>
       </c>
     </row>
     <row r="56">
@@ -3680,24 +4425,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital related to operations</t>
+          <t>Adjustment for items not involving cash</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Deferred revenue</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>ChangeInOtherWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>2.757112</v>
+          <t>Deferred income tax expense (recovery)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>2.828289</v>
+        <v>-0.1359</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.042646</v>
       </c>
     </row>
     <row r="57">
@@ -3708,24 +4454,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital related to operations</t>
+          <t>Adjustment for items not involving cash</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Net cash provided by operating activities</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>6.635791</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>9.736395</v>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-0.060129</v>
       </c>
     </row>
     <row r="58">
@@ -3736,20 +4485,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustment for items not involving cash</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Digital currency</t>
+          <t>Loss on investments</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" s="5" t="n">
-        <v>0.2255</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.7681789999999999</v>
+        <v>0.50292</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.5401010000000001</v>
       </c>
     </row>
     <row r="59">
@@ -3760,24 +4514,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustment for items not involving cash</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sale of investments</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SaleOfInvestment</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>0.584221</v>
+          <t>Realized gain on digital currency</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.008722000000000001</v>
+        <v>-1.073739</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-1.214867</v>
       </c>
     </row>
     <row r="60">
@@ -3788,24 +4543,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustment for items not involving cash</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Purchase of investments</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>PurchaseOfInvestment</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>-0.792408</v>
+          <t>Share of loss from investment in joint venture</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.971982</v>
+        <v>0.321469</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.619378</v>
       </c>
     </row>
     <row r="61">
@@ -3816,20 +4572,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustment for items not involving cash</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Purchase of equipment</t>
+          <t>Loss from equity pick-up</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" s="5" t="n">
-        <v>-0.04295</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>-0.092699</v>
+        <v>0.635167</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.757356</v>
       </c>
     </row>
     <row r="62">
@@ -3840,20 +4601,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustment for items not involving cash</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Purchase of other intangible assets</t>
+          <t>Fair value of shares issued as finder’s fees for business combination</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" s="5" t="n">
-        <v>-0.171225</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>-1.087814</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.111038</v>
       </c>
     </row>
     <row r="63">
@@ -3864,20 +4632,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustment for items not involving cash</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Convertible debenture receivable</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" s="5" t="n">
-        <v>-0.099999</v>
+          <t>Share-based payment</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>-0.7475000000000001</v>
+        <v>0.10742</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>1.307359</v>
       </c>
     </row>
     <row r="64">
@@ -3888,20 +4665,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustment for items not involving cash</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Promissory notes receivable</t>
+          <t>Adjustment for items not involving cash total</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" s="5" t="n">
-        <v>-0.54889</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>-1.79706</v>
+        <v>1.897735</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>5.153321</v>
       </c>
     </row>
     <row r="65">
@@ -3912,22 +4694,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash working capital related to operations</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Acquisition of SewerVUE</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>-2.45</v>
+        <v>-0.302286</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.558439</v>
       </c>
     </row>
     <row r="66">
@@ -3938,24 +4727,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash working capital related to operations</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>-0.845751</v>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-6.370154</v>
+        <v>-0.121541</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>-0.107756</v>
       </c>
     </row>
     <row r="67">
@@ -3966,12 +4760,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital related to operations</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Exercise of options</t>
+          <t>Registry deposits</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -3981,7 +4775,10 @@
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.022</v>
+        <v>0.746143</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.333685</v>
       </c>
     </row>
     <row r="68">
@@ -3992,20 +4789,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital related to operations</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Share repurchases</t>
+          <t>Prepaid domain name registry fees</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" s="5" t="n">
-        <v>-0.324334</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.408951</v>
+        <v>-1.585685</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>-2.030761</v>
       </c>
     </row>
     <row r="69">
@@ -4016,20 +4818,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital related to operations</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Distributions to non-controlling interest</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" s="5" t="n">
-        <v>-1.393471</v>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>-1.60395</v>
+        <v>2.033109</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>2.145001</v>
       </c>
     </row>
     <row r="70">
@@ -4040,20 +4851,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital related to operations</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Loan repayment, net of loan proceeds</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" s="5" t="n">
-        <v>-3.503713</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>-0.536498</v>
+        <v>1.211204</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.856177</v>
       </c>
     </row>
     <row r="71">
@@ -4064,22 +4880,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital related to operations</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lease payment</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Deferred revenue</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ChangeInOtherWorkingCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>-0.019755</v>
+        <v>2.757112</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>2.828289</v>
       </c>
     </row>
     <row r="72">
@@ -4090,24 +4913,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital related to operations</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Net cash used in financing activities</t>
+          <t>Net cash provided by operating activities</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>-5.221518</v>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-2.547154</v>
+        <v>6.635791</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>9.736395</v>
       </c>
     </row>
     <row r="73">
@@ -4118,20 +4946,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Foreign exchange on cash</t>
+          <t>Digital currency</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" s="5" t="n">
-        <v>0.055309</v>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-0.221861</v>
+        <v>0.2255</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.7681789999999999</v>
       </c>
     </row>
     <row r="74">
@@ -4142,20 +4975,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Increase in cash during the year</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" s="5" t="n">
-        <v>0.623831</v>
+          <t>Sale of investments</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.597226</v>
+        <v>0.584221</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.008722000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -4166,24 +5008,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cash – beginning of the year</t>
+          <t>Purchase of investments</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>2.379275</v>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>3.003106</v>
+        <v>-0.792408</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>-0.971982</v>
       </c>
     </row>
     <row r="76">
@@ -4194,24 +5041,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cash – end of the year</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>3.003106</v>
+          <t>Purchase of equipment</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>3.600332</v>
+        <v>-0.04295</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>-0.092699</v>
       </c>
     </row>
     <row r="77">
@@ -4222,20 +5070,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cash paid for interest</t>
+          <t>Purchase of other intangible assets</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" s="5" t="n">
-        <v>-0.392556</v>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>-0.048968</v>
+        <v>-0.171225</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>-1.087814</v>
       </c>
     </row>
     <row r="78">
@@ -4246,20 +5099,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cash paid for income tax</t>
+          <t>Convertible debenture receivable</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="n">
-        <v>-0.932611</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-1.657125</v>
+        <v>-0.099999</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>-0.7475000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -4270,12 +5128,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1. NATURE OF OPERATIONS AND GOING CONCERN</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>with limited liability under the legislation of the Province of British Columbia. The Company’s shares are listed on the Canadian Securities Exchange (“CSE”). The head office and principal address is</t>
+          <t>Promissory notes receivable</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -4285,7 +5143,10 @@
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.54889</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>-1.79706</v>
       </c>
     </row>
     <row r="80">
@@ -4296,416 +5157,484 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Percentage owned</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Incorporated in Status Dec 31, 2025 Dec</t>
+          <t>Acquisition of SewerVUE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>-2.45</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>REVENUE 16</t>
+          <t>Net cash used in investing activities</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="n">
-        <v>55.233043</v>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>65.468311</v>
+        <v>-0.845751</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>-6.370154</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>-43.152984</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>-48.735851</v>
+          <t>Exercise of options</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.022</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GROSS PROFIT</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>12.080059</v>
+          <t>Share repurchases</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>16.73246</v>
+        <v>-0.324334</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>-0.408951</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Amortization 10, 11, 12</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="n">
-        <v>1.015601</v>
+          <t>Distributions to non-controlling interest</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.7758659999999999</v>
+        <v>-1.393471</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>-1.60395</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Contractor fees</t>
+          <t>Loan repayment, net of loan proceeds</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" s="5" t="n">
-        <v>0.895686</v>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>1.665438</v>
+        <v>-3.503713</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>-0.536498</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Management fees 23</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>0.36</v>
+          <t>Lease payment</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>-0.019755</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" s="5" t="n">
-        <v>0.465319</v>
+          <t>Net cash used in financing activities</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0.346849</v>
+        <v>-5.221518</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>-2.547154</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Merchant fees</t>
+          <t>Foreign exchange on cash</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" s="5" t="n">
-        <v>2.28553</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>2.240918</v>
+        <v>0.055309</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>-0.221861</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Office and general</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="n">
-        <v>0.686766</v>
+          <t>Increase in cash during the year</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.735916</v>
+        <v>0.623831</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.597226</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Product development costs</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" s="5" t="n">
-        <v>1.574506</v>
+          <t>Cash – beginning of the year</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>1.928529</v>
+        <v>2.379275</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>3.003106</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Professional fees 23</t>
+          <t>Cash – end of the year</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="n">
-        <v>0.442415</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.472305</v>
+        <v>3.003106</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>3.600332</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Salaries</t>
+          <t>Cash paid for interest</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" s="5" t="n">
-        <v>0.276525</v>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.372086</v>
+        <v>-0.392556</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>-0.048968</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="n">
-        <v>8.002348</v>
+          <t>Cash paid for income tax</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>8.897907</v>
+        <v>-0.932611</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>-1.657125</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>1.    NATURE OF OPERATIONS AND GOING CONCERN</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Income before other items</t>
+          <t>with limited liability under the legislation of the Province of British Columbia. The Company’s shares are listed on the Canadian Securities Exchange (“CSE”). The head office and principal address is</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" s="5" t="n">
-        <v>4.077711</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>7.834553</v>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.0011</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Percentage owned</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="n">
-        <v>0.140485</v>
+          <t>Incorporated in Status Dec 31, 2025 Dec</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.094336</v>
+        <v>0.002024</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="96">
@@ -4716,20 +5645,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Interest and accretion expense 18, 19, 20</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" s="5" t="n">
-        <v>-0.612475</v>
+          <t>REVENUE 16</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.116768</v>
+        <v>55.233043</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>65.468311</v>
       </c>
     </row>
     <row r="97">
@@ -4740,24 +5678,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0.02418</v>
+        <v>40.083586</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.315796</v>
+        <v>43.152984</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>48.735851</v>
       </c>
     </row>
     <row r="98">
@@ -4768,20 +5709,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Realized gain on digital currency 4</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>GROSS PROFIT</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
-        <v>1.073739</v>
+        <v>8.879213</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>1.214867</v>
+        <v>12.080059</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>16.73246</v>
       </c>
     </row>
     <row r="99">
@@ -4792,20 +5740,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Loss on investments 5</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" s="5" t="n">
-        <v>-0.50292</v>
+          <t>Amortization 10, 11, 12</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>-0.5401010000000001</v>
+        <v>1.015601</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.7758659999999999</v>
       </c>
     </row>
     <row r="100">
@@ -4816,20 +5773,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Share of loss from investment in joint venture 8</t>
+          <t>Contractor fees</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" s="5" t="n">
-        <v>-0.321469</v>
+        <v>1.992169</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>-0.619378</v>
+        <v>0.895686</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>1.665438</v>
       </c>
     </row>
     <row r="101">
@@ -4840,20 +5800,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Loss from equity pick-up 9</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" s="5" t="n">
-        <v>-0.635167</v>
+          <t>Management fees 23</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>-0.757356</v>
+        <v>0.36</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="102">
@@ -4864,24 +5833,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Other expense 15</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>-1.85637</v>
+        <v>0.225953</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-1.380181</v>
+        <v>0.465319</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.346849</v>
       </c>
     </row>
     <row r="103">
@@ -4892,20 +5864,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Share-based payment 21, 23</t>
+          <t>Merchant fees</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" s="5" t="n">
-        <v>-0.10742</v>
+        <v>1.566234</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>-1.307359</v>
+        <v>2.28553</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>2.240918</v>
       </c>
     </row>
     <row r="104">
@@ -4916,20 +5891,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>OTHER ITEMS total</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E104" s="5" t="n">
-        <v>-2.797417</v>
+        <v>0.489609</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-3.096144</v>
+        <v>0.686766</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.735916</v>
       </c>
     </row>
     <row r="105">
@@ -4940,24 +5922,23 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Income before income tax</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Product development costs</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" s="5" t="n">
-        <v>1.280294</v>
+        <v>0.613791</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>4.738409</v>
+        <v>1.574506</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>1.928529</v>
       </c>
     </row>
     <row r="106">
@@ -4968,24 +5949,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Income tax expense 28</t>
+          <t>Professional fees 23</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="n">
-        <v>-0.9754159999999999</v>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F106" s="5" t="n">
-        <v>-2.546148</v>
+        <v>0.442415</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.472305</v>
       </c>
     </row>
     <row r="107">
@@ -4996,24 +5982,23 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Salaries</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" s="5" t="n">
-        <v>0.304878</v>
+        <v>0.231483</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>2.192261</v>
+        <v>0.276525</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.372086</v>
       </c>
     </row>
     <row r="108">
@@ -5024,20 +6009,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Digital currency revaluation</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
+          <t>GENERAL AND ADMINISTRATION EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E108" s="5" t="n">
-        <v>-0.09920900000000001</v>
+        <v>7.010865</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.185589</v>
+        <v>8.002348</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>8.897907</v>
       </c>
     </row>
     <row r="109">
@@ -5048,20 +6040,23 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Exchange difference on subsidiary translation</t>
+          <t>Income before other items</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" s="5" t="n">
-        <v>-0.138813</v>
+        <v>1.868348</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>0.073327</v>
+        <v>4.077711</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>7.834553</v>
       </c>
     </row>
     <row r="110">
@@ -5072,20 +6067,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Total comprehensive income</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E110" s="5" t="n">
-        <v>0.066856</v>
+        <v>-0.049132</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>2.451177</v>
+        <v>0.140485</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.094336</v>
       </c>
     </row>
     <row r="111">
@@ -5096,20 +6098,25 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Income (loss) attributable to</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Shareholders of the Company</t>
+          <t>Interest and accretion expense 18, 19, 20</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" s="5" t="n">
-        <v>-0.343137</v>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F111" s="5" t="n">
-        <v>0.951839</v>
+        <v>-0.612475</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>-0.116768</v>
       </c>
     </row>
     <row r="112">
@@ -5120,24 +6127,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Income (loss) attributable to</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Non-controlling interest</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>-0.648015</v>
+        <v>0.0003</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>-1.240422</v>
+        <v>0.02418</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.315796</v>
       </c>
     </row>
     <row r="113">
@@ -5148,20 +6158,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Income (loss) attributable to</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Income (loss) attributable to total</t>
+          <t>Realized gain on digital currency 4</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" s="5" t="n">
-        <v>0.304878</v>
+        <v>0.325702</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>2.192261</v>
+        <v>1.073739</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>1.214867</v>
       </c>
     </row>
     <row r="114">
@@ -5172,20 +6185,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Shareholders of the Company</t>
+          <t>Loss on investments 5</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" s="5" t="n">
-        <v>-0.537125</v>
+        <v>-2.3421</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>1.162855</v>
+        <v>-0.50292</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>-0.5401010000000001</v>
       </c>
     </row>
     <row r="115">
@@ -5196,24 +6212,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Non-controlling interest</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="n">
-        <v>-0.603981</v>
+          <t>Share of loss from investment in joint venture 8</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F115" s="5" t="n">
-        <v>-1.288322</v>
+        <v>-0.321469</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>-0.619378</v>
       </c>
     </row>
     <row r="116">
@@ -5224,20 +6241,25 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to total</t>
+          <t>Loss from equity pick-up 9</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" s="5" t="n">
-        <v>0.066856</v>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F116" s="5" t="n">
-        <v>2.451177</v>
+        <v>-0.635167</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>-0.757356</v>
       </c>
     </row>
     <row r="117">
@@ -5248,20 +6270,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Basic income per share</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" s="5" t="n">
-        <v>0</v>
+          <t>Other expense 15</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F117" s="5" t="n">
-        <v>2e-08</v>
+        <v>-1.85637</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>-1.380181</v>
       </c>
     </row>
     <row r="118">
@@ -5272,24 +6303,25 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Diluted income per share</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="n">
-        <v>0</v>
+          <t>Share-based payment 21, 23</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F118" s="5" t="n">
-        <v>2e-08</v>
+        <v>-0.10742</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>-1.307359</v>
       </c>
     </row>
     <row r="119">
@@ -5300,24 +6332,23 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding – basic</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>OTHER ITEMS total</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" s="5" t="n">
-        <v>89.70419200000001</v>
+        <v>-3.579123</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>88.08009199999999</v>
+        <v>-2.797417</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>-3.096144</v>
       </c>
     </row>
     <row r="120">
@@ -5328,20 +6359,1009 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Income before income tax</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>1.280294</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>4.738409</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Income tax expense 28</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>-0.9754159999999999</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>-2.546148</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0.304878</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>2.192261</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Digital currency revaluation</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>-0.09920900000000001</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>0.185589</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Exchange difference on subsidiary translation</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>-0.138813</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>0.073327</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>0.066856</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>2.451177</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Shareholders of the Company</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" s="5" t="n">
+        <v>-1.814501</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>-0.343137</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>0.951839</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Non-controlling interest</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="n">
+        <v>-0.529863</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>-0.648015</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>-1.240422</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Income (loss) attributable to total</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" s="5" t="n">
+        <v>-1.284638</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>0.304878</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>2.192261</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
           <t>Comprehensive income (loss) attributable to</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Shareholders of the Company</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" s="5" t="n">
+        <v>-1.940038</v>
+      </c>
+      <c r="F129" s="5" t="n">
+        <v>-0.537125</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>1.162855</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Non-controlling interest</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="n">
+        <v>-0.501366</v>
+      </c>
+      <c r="F130" s="5" t="n">
+        <v>-0.603981</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>-1.288322</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Comprehensive income (loss) attributable to total</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" s="5" t="n">
+        <v>-1.438672</v>
+      </c>
+      <c r="F131" s="5" t="n">
+        <v>0.066856</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>2.451177</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Basic income per share</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Diluted income per share</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>2e-08</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding – basic</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>91.255689</v>
+      </c>
+      <c r="F134" s="5" t="n">
+        <v>89.70419200000001</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>88.08009199999999</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
         <is>
           <t>Weighted average number of shares outstanding – diluted</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" s="5" t="n">
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" s="5" t="n">
+        <v>91.255689</v>
+      </c>
+      <c r="F135" s="5" t="n">
         <v>95.479192</v>
       </c>
-      <c r="F120" s="5" t="n">
+      <c r="G135" s="5" t="n">
         <v>92.357463</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>REVENUE 15</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="n">
+        <v>48.962799</v>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>55.233043</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Amortization 9, 10, 12</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>1.102392</v>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>1.015601</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Management fees 20</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Professional fees 20</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="n">
+        <v>0.429234</v>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>0.442415</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Interest and accretion expense 16, 17</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" s="5" t="n">
+        <v>-0.703691</v>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>-0.612475</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Share of loss from investment in joint venture 7</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>-0.321469</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Loss from equity pick-up 8</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" s="5" t="n">
+        <v>-0.15391</v>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>-0.635167</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Other expense 14</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>-0.656292</v>
+      </c>
+      <c r="F143" s="5" t="n">
+        <v>-1.85637</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Share-based payment 18, 20</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="n">
+        <v>-0.10742</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Income (loss) before income tax</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>-1.710775</v>
+      </c>
+      <c r="F145" s="5" t="n">
+        <v>1.280294</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Income tax (expense) recovery 25</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="n">
+        <v>0.426137</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>-0.9754159999999999</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Net income (loss)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>-1.284638</v>
+      </c>
+      <c r="F147" s="5" t="n">
+        <v>0.304878</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Digital currency revaluation</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" s="5" t="n">
+        <v>-0.09417</v>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>-0.09920900000000001</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Exchange difference on subsidiary translation</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" s="5" t="n">
+        <v>-0.059864</v>
+      </c>
+      <c r="F149" s="5" t="n">
+        <v>-0.138813</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Total comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" s="5" t="n">
+        <v>-1.438672</v>
+      </c>
+      <c r="F150" s="5" t="n">
+        <v>0.066856</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Basic income (loss) per share</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F151" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Diluted income (loss) per share</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/pdf_financials_xlsx/URL.xlsx
+++ b/output/pdf_financials_xlsx/URL.xlsx
@@ -2497,7 +2497,7 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.019755</v>
       </c>
     </row>
     <row r="125">
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.019755</v>
       </c>
     </row>
     <row r="126">
@@ -5347,7 +5347,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/URL.xlsx
+++ b/output/pdf_financials_xlsx/URL.xlsx
@@ -2038,10 +2038,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-1.284638</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>0.304878</v>
@@ -2056,10 +2054,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -2074,10 +2070,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.048313</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.302286</v>
@@ -2092,10 +2086,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -2110,10 +2102,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>-0.000189</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>-0.121541</v>
@@ -2128,10 +2118,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>-0.348121</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>2.033109</v>
@@ -2146,10 +2134,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0.678453</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>2.757112</v>
@@ -2164,10 +2150,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.28183</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>4.366394</v>
@@ -2182,10 +2166,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0.10742</v>
@@ -2200,10 +2182,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -2218,10 +2198,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -2236,16 +2214,14 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0.234408</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.219919</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.082312</v>
       </c>
     </row>
     <row r="111">
@@ -2254,16 +2230,14 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.04295</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.092699</v>
       </c>
     </row>
     <row r="112">
@@ -2272,10 +2246,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -2290,10 +2262,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -2308,10 +2278,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>-1.065</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>-0.792408</v>
@@ -2326,10 +2294,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0.150626</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0.584221</v>
@@ -2344,16 +2310,14 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.171225</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-1.087814</v>
       </c>
     </row>
     <row r="117">
@@ -2362,10 +2326,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -2380,10 +2342,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -2398,10 +2358,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-0.914374</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>-0.845751</v>
@@ -2416,10 +2374,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -2434,16 +2390,14 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>-0.120198</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.324334</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.408951</v>
       </c>
     </row>
     <row r="122">
@@ -2452,10 +2406,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -2470,10 +2422,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -2488,10 +2438,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2506,10 +2454,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -2524,10 +2470,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -2564,10 +2508,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -2582,10 +2524,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>-0.870007</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>-5.221518</v>
@@ -2600,10 +2540,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>1.203008</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>2.379275</v>
@@ -2618,10 +2556,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -2636,10 +2572,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>1.176267</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>0.623831</v>
@@ -2654,10 +2588,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>2.379275</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>3.003106</v>
@@ -2672,16 +2604,14 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.04295</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.092699</v>
       </c>
     </row>
     <row r="135">
@@ -2690,16 +2620,14 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>2.778974</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>6.635791</v>
+        <v>6.592841</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>9.736395</v>
+        <v>9.643696</v>
       </c>
     </row>
   </sheetData>
@@ -2713,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4371,11 +4299,13 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>0.234408</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>0.219919</v>
@@ -4405,10 +4335,8 @@
           <t>Amortization</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E55" s="5" t="n">
+        <v>1.102392</v>
       </c>
       <c r="F55" s="5" t="n">
         <v>1.015601</v>
@@ -4433,7 +4361,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -4494,10 +4426,8 @@
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E58" s="5" t="n">
+        <v>2.3421</v>
       </c>
       <c r="F58" s="5" t="n">
         <v>0.50292</v>
@@ -4523,10 +4453,8 @@
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E59" s="5" t="n">
+        <v>-0.325702</v>
       </c>
       <c r="F59" s="5" t="n">
         <v>-1.073739</v>
@@ -4581,10 +4509,8 @@
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E61" s="5" t="n">
+        <v>0.15391</v>
       </c>
       <c r="F61" s="5" t="n">
         <v>0.635167</v>
@@ -4674,10 +4600,8 @@
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="5" t="n">
+        <v>1.120355</v>
       </c>
       <c r="F64" s="5" t="n">
         <v>1.897735</v>
@@ -4707,10 +4631,8 @@
           <t>ChangeInReceivables</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E65" s="5" t="n">
+        <v>-0.048313</v>
       </c>
       <c r="F65" s="5" t="n">
         <v>-0.302286</v>
@@ -4740,10 +4662,8 @@
           <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" s="5" t="n">
+        <v>-0.000189</v>
       </c>
       <c r="F66" s="5" t="n">
         <v>-0.121541</v>
@@ -4769,10 +4689,8 @@
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E67" s="5" t="n">
+        <v>-0.5147699999999999</v>
       </c>
       <c r="F67" s="5" t="n">
         <v>0.746143</v>
@@ -4798,10 +4716,8 @@
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E68" s="5" t="n">
+        <v>1.019732</v>
       </c>
       <c r="F68" s="5" t="n">
         <v>-1.585685</v>
@@ -4831,10 +4747,8 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" s="5" t="n">
+        <v>-0.348121</v>
       </c>
       <c r="F69" s="5" t="n">
         <v>2.033109</v>
@@ -4860,10 +4774,8 @@
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E70" s="5" t="n">
+        <v>0.6859690000000001</v>
       </c>
       <c r="F70" s="5" t="n">
         <v>1.211204</v>
@@ -4893,10 +4805,8 @@
           <t>ChangeInOtherWorkingCapital</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E71" s="5" t="n">
+        <v>0.678453</v>
       </c>
       <c r="F71" s="5" t="n">
         <v>2.757112</v>
@@ -4926,10 +4836,8 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E72" s="5" t="n">
+        <v>2.778974</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>6.635791</v>
@@ -4955,10 +4863,8 @@
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E73" s="5" t="n">
+        <v>0.185858</v>
       </c>
       <c r="F73" s="5" t="n">
         <v>0.2255</v>
@@ -4988,10 +4894,8 @@
           <t>SaleOfInvestment</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E74" s="5" t="n">
+        <v>0.150626</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>0.584221</v>
@@ -5021,10 +4925,8 @@
           <t>PurchaseOfInvestment</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E75" s="5" t="n">
+        <v>-1.065</v>
       </c>
       <c r="F75" s="5" t="n">
         <v>-0.792408</v>
@@ -5049,7 +4951,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -5078,7 +4984,11 @@
           <t>Purchase of other intangible assets</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -5201,10 +5111,8 @@
           <t>InvestingCashFlow</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E81" s="5" t="n">
+        <v>-0.914374</v>
       </c>
       <c r="F81" s="5" t="n">
         <v>-0.845751</v>
@@ -5260,11 +5168,13 @@
           <t>Share repurchases</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>-0.120198</v>
       </c>
       <c r="F83" s="5" t="n">
         <v>-0.324334</v>
@@ -5290,10 +5200,8 @@
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E84" s="5" t="n">
+        <v>-0.7498089999999999</v>
       </c>
       <c r="F84" s="5" t="n">
         <v>-1.393471</v>
@@ -5387,10 +5295,8 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E87" s="5" t="n">
+        <v>-0.870007</v>
       </c>
       <c r="F87" s="5" t="n">
         <v>-5.221518</v>
@@ -5416,10 +5322,8 @@
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E88" s="5" t="n">
+        <v>0.181674</v>
       </c>
       <c r="F88" s="5" t="n">
         <v>0.055309</v>
@@ -5445,10 +5349,8 @@
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E89" s="5" t="n">
+        <v>1.176267</v>
       </c>
       <c r="F89" s="5" t="n">
         <v>0.623831</v>
@@ -5478,10 +5380,8 @@
           <t>BeginningCashPosition</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E90" s="5" t="n">
+        <v>1.203008</v>
       </c>
       <c r="F90" s="5" t="n">
         <v>2.379275</v>
@@ -5511,10 +5411,8 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E91" s="5" t="n">
+        <v>2.379275</v>
       </c>
       <c r="F91" s="5" t="n">
         <v>3.003106</v>
@@ -5540,10 +5438,8 @@
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E92" s="5" t="n">
+        <v>-0.469283</v>
       </c>
       <c r="F92" s="5" t="n">
         <v>-0.392556</v>
@@ -5569,10 +5465,8 @@
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E93" s="5" t="n">
+        <v>-0.375274</v>
       </c>
       <c r="F93" s="5" t="n">
         <v>-0.932611</v>
@@ -5644,156 +5538,158 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>REVENUE 16</t>
+          <t>Net income (loss) for the year</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>-1.284638</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>55.233043</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>65.468311</v>
+        <v>0.304878</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Adjustment for items not involving cash</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>COST OF SALES</t>
+          <t>Deferred income tax recovery</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
+          <t>DeferredTax</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>40.083586</v>
+        <v>-1.102115</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>43.152984</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>48.735851</v>
+        <v>-0.1359</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GROSS PROFIT</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>8.879213</v>
+          <t>Loan repayment</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>12.080059</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>16.73246</v>
+        <v>-4.9</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Amortization 10, 11, 12</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Loan proceeds</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>1.015601</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>0.7758659999999999</v>
+        <v>1.396287</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Percentage owned</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Contractor fees</t>
+          <t>Incorporated Status Dec 31, 2024 Dec</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" s="5" t="n">
-        <v>1.992169</v>
+        <v>0.002023</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.895686</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>1.665438</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -5804,17 +5700,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Management fees 23</t>
+          <t>REVENUE 16</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5823,10 +5719,10 @@
         </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>0.36</v>
+        <v>55.233043</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.36</v>
+        <v>65.468311</v>
       </c>
     </row>
     <row r="102">
@@ -5837,27 +5733,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>COST OF SALES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0.225953</v>
+        <v>40.083586</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.465319</v>
+        <v>43.152984</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.346849</v>
+        <v>48.735851</v>
       </c>
     </row>
     <row r="103">
@@ -5868,23 +5764,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Merchant fees</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>GROSS PROFIT</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
-        <v>1.566234</v>
+        <v>8.879213</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>2.28553</v>
+        <v>12.080059</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>2.240918</v>
+        <v>16.73246</v>
       </c>
     </row>
     <row r="104">
@@ -5900,22 +5800,24 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Office and general</t>
+          <t>Amortization 10, 11, 12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="n">
-        <v>0.489609</v>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.686766</v>
+        <v>1.015601</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.735916</v>
+        <v>0.7758659999999999</v>
       </c>
     </row>
     <row r="105">
@@ -5931,18 +5833,18 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Product development costs</t>
+          <t>Contractor fees</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" s="5" t="n">
-        <v>0.613791</v>
+        <v>1.992169</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>1.574506</v>
+        <v>0.895686</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>1.928529</v>
+        <v>1.665438</v>
       </c>
     </row>
     <row r="106">
@@ -5958,12 +5860,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Professional fees 23</t>
+          <t>Management fees 23</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5972,10 +5874,10 @@
         </is>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.442415</v>
+        <v>0.36</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.472305</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="107">
@@ -5991,18 +5893,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Salaries</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E107" s="5" t="n">
-        <v>0.231483</v>
+        <v>0.225953</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.276525</v>
+        <v>0.465319</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.372086</v>
+        <v>0.346849</v>
       </c>
     </row>
     <row r="108">
@@ -6018,22 +5924,18 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Merchant fees</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" s="5" t="n">
-        <v>7.010865</v>
+        <v>1.566234</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>8.002348</v>
+        <v>2.28553</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>8.897907</v>
+        <v>2.240918</v>
       </c>
     </row>
     <row r="109">
@@ -6049,18 +5951,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Income before other items</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E109" s="5" t="n">
-        <v>1.868348</v>
+        <v>0.489609</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>4.077711</v>
+        <v>0.686766</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>7.834553</v>
+        <v>0.735916</v>
       </c>
     </row>
     <row r="110">
@@ -6071,27 +5977,23 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Product development costs</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" s="5" t="n">
-        <v>-0.049132</v>
+        <v>0.613791</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.140485</v>
+        <v>1.574506</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.094336</v>
+        <v>1.928529</v>
       </c>
     </row>
     <row r="111">
@@ -6102,25 +6004,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Interest and accretion expense 18, 19, 20</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>Professional fees 23</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
-        <v>-0.612475</v>
+        <v>0.442415</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>-0.116768</v>
+        <v>0.472305</v>
       </c>
     </row>
     <row r="112">
@@ -6131,27 +6037,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Salaries</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.231483</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.02418</v>
+        <v>0.276525</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.315796</v>
+        <v>0.372086</v>
       </c>
     </row>
     <row r="113">
@@ -6162,23 +6064,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Realized gain on digital currency 4</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
+          <t>GENERAL AND ADMINISTRATION EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E113" s="5" t="n">
-        <v>0.325702</v>
+        <v>7.010865</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>1.073739</v>
+        <v>8.002348</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1.214867</v>
+        <v>8.897907</v>
       </c>
     </row>
     <row r="114">
@@ -6189,23 +6095,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Loss on investments 5</t>
+          <t>Income before other items</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" s="5" t="n">
-        <v>-2.3421</v>
+        <v>1.868348</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>-0.50292</v>
+        <v>4.077711</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>-0.5401010000000001</v>
+        <v>7.834553</v>
       </c>
     </row>
     <row r="115">
@@ -6221,20 +6127,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Share of loss from investment in joint venture 8</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>-0.049132</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>-0.321469</v>
+        <v>0.140485</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>-0.619378</v>
+        <v>0.094336</v>
       </c>
     </row>
     <row r="116">
@@ -6250,7 +6158,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Loss from equity pick-up 9</t>
+          <t>Interest and accretion expense 18, 19, 20</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -6260,10 +6168,10 @@
         </is>
       </c>
       <c r="F116" s="5" t="n">
-        <v>-0.635167</v>
+        <v>-0.612475</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>-0.757356</v>
+        <v>-0.116768</v>
       </c>
     </row>
     <row r="117">
@@ -6279,7 +6187,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Other expense 15</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6287,16 +6195,14 @@
           <t>OtherIncomeExpense</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E117" s="5" t="n">
+        <v>0.0003</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>-1.85637</v>
+        <v>0.02418</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>-1.380181</v>
+        <v>0.315796</v>
       </c>
     </row>
     <row r="118">
@@ -6312,20 +6218,18 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Share-based payment 21, 23</t>
+          <t>Realized gain on digital currency 4</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E118" s="5" t="n">
+        <v>0.325702</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>-0.10742</v>
+        <v>1.073739</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>-1.307359</v>
+        <v>1.214867</v>
       </c>
     </row>
     <row r="119">
@@ -6341,18 +6245,18 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>OTHER ITEMS total</t>
+          <t>Loss on investments 5</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" s="5" t="n">
-        <v>-3.579123</v>
+        <v>-2.3421</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>-2.797417</v>
+        <v>-0.50292</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>-3.096144</v>
+        <v>-0.5401010000000001</v>
       </c>
     </row>
     <row r="120">
@@ -6368,24 +6272,20 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Income before income tax</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Share of loss from investment in joint venture 8</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F120" s="5" t="n">
-        <v>1.280294</v>
+        <v>-0.321469</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>4.738409</v>
+        <v>-0.619378</v>
       </c>
     </row>
     <row r="121">
@@ -6401,24 +6301,20 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Income tax expense 28</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Loss from equity pick-up 9</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
-        <v>-0.9754159999999999</v>
+        <v>-0.635167</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>-2.546148</v>
+        <v>-0.757356</v>
       </c>
     </row>
     <row r="122">
@@ -6434,12 +6330,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Net income</t>
+          <t>Other expense 15</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6448,10 +6344,10 @@
         </is>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.304878</v>
+        <v>-1.85637</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>2.192261</v>
+        <v>-1.380181</v>
       </c>
     </row>
     <row r="123">
@@ -6462,12 +6358,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Digital currency revaluation</t>
+          <t>Share-based payment 21, 23</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -6477,10 +6373,10 @@
         </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>-0.09920900000000001</v>
+        <v>-0.10742</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.185589</v>
+        <v>-1.307359</v>
       </c>
     </row>
     <row r="124">
@@ -6491,25 +6387,23 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Exchange difference on subsidiary translation</t>
+          <t>OTHER ITEMS total</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E124" s="5" t="n">
+        <v>-3.579123</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>-0.138813</v>
+        <v>-2.797417</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.073327</v>
+        <v>-3.096144</v>
       </c>
     </row>
     <row r="125">
@@ -6520,25 +6414,29 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Total comprehensive income</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
+          <t>Income before income tax</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F125" s="5" t="n">
-        <v>0.066856</v>
+        <v>1.280294</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>2.451177</v>
+        <v>4.738409</v>
       </c>
     </row>
     <row r="126">
@@ -6549,23 +6447,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Income (loss) attributable to</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Shareholders of the Company</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" s="5" t="n">
-        <v>-1.814501</v>
+          <t>Income tax expense 28</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F126" s="5" t="n">
-        <v>-0.343137</v>
+        <v>-0.9754159999999999</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.951839</v>
+        <v>-2.546148</v>
       </c>
     </row>
     <row r="127">
@@ -6576,27 +6480,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Income (loss) attributable to</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Non-controlling interest</t>
+          <t>Net income</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="n">
-        <v>-0.529863</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F127" s="5" t="n">
-        <v>-0.648015</v>
+        <v>0.304878</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>-1.240422</v>
+        <v>2.192261</v>
       </c>
     </row>
     <row r="128">
@@ -6607,23 +6513,25 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Income (loss) attributable to</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Income (loss) attributable to total</t>
+          <t>Digital currency revaluation</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" s="5" t="n">
-        <v>-1.284638</v>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0.304878</v>
+        <v>-0.09920900000000001</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>2.192261</v>
+        <v>0.185589</v>
       </c>
     </row>
     <row r="129">
@@ -6634,23 +6542,25 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Shareholders of the Company</t>
+          <t>Exchange difference on subsidiary translation</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" s="5" t="n">
-        <v>-1.940038</v>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F129" s="5" t="n">
-        <v>-0.537125</v>
+        <v>-0.138813</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>1.162855</v>
+        <v>0.073327</v>
       </c>
     </row>
     <row r="130">
@@ -6661,27 +6571,25 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Non-controlling interest</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="n">
-        <v>-0.501366</v>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F130" s="5" t="n">
-        <v>-0.603981</v>
+        <v>0.066856</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>-1.288322</v>
+        <v>2.451177</v>
       </c>
     </row>
     <row r="131">
@@ -6692,23 +6600,23 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>Income (loss) attributable to</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to total</t>
+          <t>Shareholders of the Company</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" s="5" t="n">
-        <v>-1.438672</v>
+        <v>-1.814501</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>0.066856</v>
+        <v>-0.343137</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>2.451177</v>
+        <v>0.951839</v>
       </c>
     </row>
     <row r="132">
@@ -6719,25 +6627,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>Income (loss) attributable to</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Basic income per share</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Non-controlling interest</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="n">
+        <v>-0.529863</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0</v>
+        <v>-0.648015</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>2e-08</v>
+        <v>-1.240422</v>
       </c>
     </row>
     <row r="133">
@@ -6748,29 +6658,23 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>Income (loss) attributable to</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Diluted income per share</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Income (loss) attributable to total</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" s="5" t="n">
+        <v>-1.284638</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>0</v>
+        <v>0.304878</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>2e-08</v>
+        <v>2.192261</v>
       </c>
     </row>
     <row r="134">
@@ -6786,22 +6690,18 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding – basic</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Shareholders of the Company</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" s="5" t="n">
-        <v>91.255689</v>
+        <v>-1.940038</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>89.70419200000001</v>
+        <v>-0.537125</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>88.08009199999999</v>
+        <v>1.162855</v>
       </c>
     </row>
     <row r="135">
@@ -6817,18 +6717,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding – diluted</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
+          <t>Non-controlling interest</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E135" s="5" t="n">
-        <v>91.255689</v>
+        <v>-0.501366</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>95.479192</v>
+        <v>-0.603981</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>92.357463</v>
+        <v>-1.288322</v>
       </c>
     </row>
     <row r="136">
@@ -6839,29 +6743,23 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Comprehensive income (loss) attributable to</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>REVENUE 15</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Comprehensive income (loss) attributable to total</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" s="5" t="n">
-        <v>48.962799</v>
+        <v>-1.438672</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>55.233043</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.066856</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>2.451177</v>
       </c>
     </row>
     <row r="137">
@@ -6872,29 +6770,25 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Comprehensive income (loss) attributable to</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Amortization 9, 10, 12</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="n">
-        <v>1.102392</v>
+          <t>Basic income per share</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F137" s="5" t="n">
-        <v>1.015601</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>2e-08</v>
       </c>
     </row>
     <row r="138">
@@ -6905,29 +6799,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Comprehensive income (loss) attributable to</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Management fees 20</t>
+          <t>Diluted income per share</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="n">
-        <v>0.36</v>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>2e-08</v>
       </c>
     </row>
     <row r="139">
@@ -6938,29 +6832,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
+          <t>Comprehensive income (loss) attributable to</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Professional fees 20</t>
+          <t>Weighted average number of shares outstanding – basic</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0.429234</v>
+        <v>91.255689</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>0.442415</v>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>89.70419200000001</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>88.08009199999999</v>
       </c>
     </row>
     <row r="140">
@@ -6971,25 +6863,23 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Comprehensive income (loss) attributable to</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Interest and accretion expense 16, 17</t>
+          <t>Weighted average number of shares outstanding – diluted</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" s="5" t="n">
-        <v>-0.703691</v>
+        <v>91.255689</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>-0.612475</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>95.479192</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>92.357463</v>
       </c>
     </row>
     <row r="141">
@@ -7000,22 +6890,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Share of loss from investment in joint venture 7</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>REVENUE 15</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>48.962799</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>-0.321469</v>
+        <v>55.233043</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7031,20 +6923,24 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Loss from equity pick-up 8</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
+          <t>Amortization 9, 10, 12</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E142" s="5" t="n">
-        <v>-0.15391</v>
+        <v>1.102392</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>-0.635167</v>
+        <v>1.015601</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -7060,24 +6956,24 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Other expense 14</t>
+          <t>Management fees 20</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>-0.656292</v>
+        <v>0.36</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>-1.85637</v>
+        <v>0.36</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -7093,22 +6989,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>GENERAL AND ADMINISTRATION EXPENSES</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Share-based payment 18, 20</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees 20</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>0.429234</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>-0.10742</v>
+        <v>0.442415</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -7129,19 +7027,15 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Income (loss) before income tax</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Interest and accretion expense 16, 17</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
       <c r="E145" s="5" t="n">
-        <v>-1.710775</v>
+        <v>-0.703691</v>
       </c>
       <c r="F145" s="5" t="n">
-        <v>1.280294</v>
+        <v>-0.612475</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -7162,19 +7056,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Income tax (expense) recovery 25</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="n">
-        <v>0.426137</v>
+          <t>Share of loss from investment in joint venture 7</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F146" s="5" t="n">
-        <v>-0.9754159999999999</v>
+        <v>-0.321469</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -7195,19 +7087,15 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Net income (loss)</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss from equity pick-up 8</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" s="5" t="n">
-        <v>-1.284638</v>
+        <v>-0.15391</v>
       </c>
       <c r="F147" s="5" t="n">
-        <v>0.304878</v>
+        <v>-0.635167</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -7223,20 +7111,24 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Digital currency revaluation</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
+          <t>Other expense 14</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E148" s="5" t="n">
-        <v>-0.09417</v>
+        <v>-0.656292</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>-0.09920900000000001</v>
+        <v>-1.85637</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -7252,20 +7144,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Exchange difference on subsidiary translation</t>
+          <t>Share-based payment 18, 20</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
-      <c r="E149" s="5" t="n">
-        <v>-0.059864</v>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F149" s="5" t="n">
-        <v>-0.138813</v>
+        <v>-0.10742</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -7281,20 +7175,24 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Total comprehensive income (loss)</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>Income (loss) before income tax</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E150" s="5" t="n">
-        <v>-1.438672</v>
+        <v>-1.710775</v>
       </c>
       <c r="F150" s="5" t="n">
-        <v>0.066856</v>
+        <v>1.280294</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -7310,24 +7208,24 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Comprehensive income (loss) attributable to</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Basic income (loss) per share</t>
+          <t>Income tax (expense) recovery 25</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>TaxProvision</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.426137</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>0</v>
+        <v>-0.9754159999999999</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -7343,26 +7241,179 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Net income (loss)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="n">
+        <v>-1.284638</v>
+      </c>
+      <c r="F152" s="5" t="n">
+        <v>0.304878</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Digital currency revaluation</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" s="5" t="n">
+        <v>-0.09417</v>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>-0.09920900000000001</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Exchange difference on subsidiary translation</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" s="5" t="n">
+        <v>-0.059864</v>
+      </c>
+      <c r="F154" s="5" t="n">
+        <v>-0.138813</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Total comprehensive income (loss)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" s="5" t="n">
+        <v>-1.438672</v>
+      </c>
+      <c r="F155" s="5" t="n">
+        <v>0.066856</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
           <t>Comprehensive income (loss) attributable to</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Basic income (loss) per share</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Comprehensive income (loss) attributable to</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
         <is>
           <t>Diluted income (loss) per share</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>DilutedEPS</t>
         </is>
       </c>
-      <c r="E152" s="5" t="n">
+      <c r="E157" s="5" t="n">
         <v>-1e-08</v>
       </c>
-      <c r="F152" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" t="inlineStr">
+      <c r="F157" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="inlineStr">
         <is>
           <t>-</t>
         </is>
